--- a/outputs/reports/random_forest/evaluation.xlsx
+++ b/outputs/reports/random_forest/evaluation.xlsx
@@ -487,37 +487,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9983927275241091</v>
+        <v>0.998978826913074</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6793103448275862</v>
+        <v>0.8523002421307506</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7606177606177607</v>
+        <v>0.8292108362779741</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7176684881602914</v>
+        <v>0.8405970149253731</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9990330395483359</v>
+        <v>0.9995318765228403</v>
       </c>
       <c r="G2" t="n">
-        <v>288254</v>
+        <v>260493</v>
       </c>
       <c r="H2" t="n">
-        <v>279</v>
+        <v>122</v>
       </c>
       <c r="I2" t="n">
-        <v>186</v>
+        <v>145</v>
       </c>
       <c r="J2" t="n">
-        <v>591</v>
+        <v>704</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9845367865663638</v>
+        <v>0.9839299458083961</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7424827721444611</v>
+        <v>0.8844066737680335</v>
       </c>
     </row>
   </sheetData>
@@ -531,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,32 +562,47 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>상위1%양성포착비율(top_1pct_recall)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>상위5%건수(top_5pct_count)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>상위5%양성비율(top_5pct_positive_rate)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>상위5%리프트(top_5pct_lift)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>상위5%양성포착비율(top_5pct_recall)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>상위10%건수(top_10pct_count)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>상위10%양성비율(top_10pct_positive_rate)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>상위10%리프트(top_10pct_lift)</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>상위10%양성포착비율(top_10pct_recall)</t>
         </is>
       </c>
     </row>
@@ -598,34 +613,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.002685700459714493</v>
+        <v>0.003247100939326255</v>
       </c>
       <c r="C2" t="n">
-        <v>2894</v>
+        <v>2615</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2474084312370421</v>
+        <v>0.3024856596558317</v>
       </c>
       <c r="E2" t="n">
-        <v>92.12063480204461</v>
+        <v>93.15560720406641</v>
       </c>
       <c r="F2" t="n">
-        <v>14466</v>
+        <v>0.9316843345111896</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05101617586063874</v>
+        <v>13074</v>
       </c>
       <c r="H2" t="n">
-        <v>18.99548241729909</v>
+        <v>0.06187853755545357</v>
       </c>
       <c r="I2" t="n">
-        <v>28931</v>
+        <v>19.0565488143688</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02599287961010681</v>
+        <v>0.9528857479387515</v>
       </c>
       <c r="K2" t="n">
-        <v>9.678249678249678</v>
+        <v>26147</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.03109343328106475</v>
+      </c>
+      <c r="M2" t="n">
+        <v>9.575751989870804</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.9575971731448764</v>
       </c>
     </row>
   </sheetData>
@@ -676,13 +700,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>277032</v>
+        <v>249760</v>
       </c>
       <c r="C2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001479973432672038</v>
+        <v>0.0001681614349775785</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -695,13 +719,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10171</v>
+        <v>9327</v>
       </c>
       <c r="C3" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002752924982794219</v>
+        <v>0.001715449769486437</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -714,13 +738,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>823</v>
+        <v>1153</v>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01822600243013366</v>
+        <v>0.01734605377276669</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -733,13 +757,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2164502164502164</v>
+        <v>0.1171875</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -752,13 +776,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>141</v>
       </c>
       <c r="C6" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2802197802197802</v>
+        <v>0.2624113475177305</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -771,13 +795,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="C7" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D7" t="n">
-        <v>0.408284023668639</v>
+        <v>0.5338983050847458</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -790,13 +814,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>185</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5567567567567567</v>
+        <v>0.66</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -809,13 +833,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>186</v>
+        <v>122</v>
       </c>
       <c r="C9" t="n">
-        <v>137</v>
+        <v>95</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7365591397849462</v>
+        <v>0.7786885245901639</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -828,13 +852,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="C10" t="n">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8</v>
+        <v>0.9634146341463414</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -847,13 +871,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>156</v>
+        <v>323</v>
       </c>
       <c r="C11" t="n">
-        <v>143</v>
+        <v>322</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9969040247678018</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
